--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -1,5 +1,1327 @@
 
-<file path=theme/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20130" windowHeight="7710"/>
+  </bookViews>
+  <sheets>
+    <sheet name="投资者身份信息维护模板" sheetId="1" r:id="rId1"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
+  </sheets>
+  <calcPr calcId="144525"/>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="332">
+  <si>
+    <t>登记银行代码*</t>
+  </si>
+  <si>
+    <t>识别标识*</t>
+  </si>
+  <si>
+    <t>原识别标识</t>
+  </si>
+  <si>
+    <t>该投资者是否属于本行</t>
+  </si>
+  <si>
+    <t>投资者所属银行名称</t>
+  </si>
+  <si>
+    <t>投资者所属银行代码</t>
+  </si>
+  <si>
+    <t>投资者境内外标识</t>
+  </si>
+  <si>
+    <t>投资者所属国家或地区</t>
+  </si>
+  <si>
+    <t>投资者类别*</t>
+  </si>
+  <si>
+    <t>个人证件类别</t>
+  </si>
+  <si>
+    <t>机构证件类别</t>
+  </si>
+  <si>
+    <t>其他证件名称</t>
+  </si>
+  <si>
+    <t>证件号码*</t>
+  </si>
+  <si>
+    <t>SPV资金托管账户开户行</t>
+  </si>
+  <si>
+    <t>其他资金托管账户开户行</t>
+  </si>
+  <si>
+    <t>投资者名称*</t>
+  </si>
+  <si>
+    <t>性别*</t>
+  </si>
+  <si>
+    <t>风险偏好*</t>
+  </si>
+  <si>
+    <t>手机号码</t>
+  </si>
+  <si>
+    <t>固定电话</t>
+  </si>
+  <si>
+    <t>电子邮箱</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>经办人</t>
+  </si>
+  <si>
+    <t>接入检查结果</t>
+  </si>
+  <si>
+    <t>中债反馈消息</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“选择性粘贴”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并只</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“粘贴数值”</t>
+    </r>
+  </si>
+  <si>
+    <t>2.必填要素请参照《数据元规范》。</t>
+  </si>
+  <si>
+    <t>数据类型的枚举值：01 新增/02 识别标识变更/03 重要信息变更/04 其他信息变更。历史数据都填01 新增即可</t>
+  </si>
+  <si>
+    <t>SPV资金托管账户开户行枚举值：</t>
+  </si>
+  <si>
+    <t>C10102 中国工商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10103 中国农业银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10104 中国银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10105 中国建设银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10301 交通银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10304 华夏银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10303 中国光大银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10308 招商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10302 中信银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10305 中国民生银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10309 兴业银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10310 上海浦东发展银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10802 北京银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10307 平安银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10306 广发银行股份有限公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10403 中国邮政储蓄银行有限责任公司 </t>
+  </si>
+  <si>
+    <t>C10912 上海银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C12112 渤海银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10921 宁波银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10316 浙商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10804 徽商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C11312 广州农村商业银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10876 包商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10315 恒丰银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10920 杭州银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10869 南京银行股份有限公司</t>
+  </si>
+  <si>
+    <t>C10868 江苏银行股份有限公司</t>
+  </si>
+  <si>
+    <t>99999 其他</t>
+  </si>
+  <si>
+    <t>机构证件类别枚举值</t>
+  </si>
+  <si>
+    <t>01 法人和其他组织统一社会信用代码</t>
+  </si>
+  <si>
+    <t>02 全国组织机构代码</t>
+  </si>
+  <si>
+    <t>03 企业法人营业执照号码</t>
+  </si>
+  <si>
+    <t>04 国税登记证号码</t>
+  </si>
+  <si>
+    <t>05 金融许可证号码</t>
+  </si>
+  <si>
+    <t>06 基本存款账户开户登记证号码</t>
+  </si>
+  <si>
+    <t>07 政府人事部门批文号码</t>
+  </si>
+  <si>
+    <t>08 编制委员会批文号码</t>
+  </si>
+  <si>
+    <t>09 政府人事部门登记证书号码</t>
+  </si>
+  <si>
+    <t>10 编制委员会登记证书号码</t>
+  </si>
+  <si>
+    <t>11 军队、武警财务部门开户证明号码</t>
+  </si>
+  <si>
+    <t>12 社会团体登记证书号码</t>
+  </si>
+  <si>
+    <t>13 民办非企业登记证书号码</t>
+  </si>
+  <si>
+    <t>14 外地常设机构住在地政府主管部门批文号码</t>
+  </si>
+  <si>
+    <t>15 国家主管部门颁外国驻华机构批文号码</t>
+  </si>
+  <si>
+    <t>16 国家登记机关颁外资企业驻华代表、办事处登记证号码</t>
+  </si>
+  <si>
+    <t>17 主管部门颁居民、村民、社区委员会批文号码</t>
+  </si>
+  <si>
+    <t>18 独立核算的附属机构批文号码</t>
+  </si>
+  <si>
+    <t>19 主管部门批文号码</t>
+  </si>
+  <si>
+    <t>20 财政部门证明号码</t>
+  </si>
+  <si>
+    <t>21 证券投资业务许可证号码</t>
+  </si>
+  <si>
+    <t>22 临时经营地工商行政管理部门批文号码</t>
+  </si>
+  <si>
+    <t>23 企业名称预先核准通知书号码</t>
+  </si>
+  <si>
+    <t>24 企业营业执照号码</t>
+  </si>
+  <si>
+    <t>25 个体工商户营业执照号码</t>
+  </si>
+  <si>
+    <t>26 地税登记证号码</t>
+  </si>
+  <si>
+    <t>27 宗教事务管理部门的批文或证明号码</t>
+  </si>
+  <si>
+    <t>28 借款合同号码</t>
+  </si>
+  <si>
+    <t>29 国家外汇管理部门的批复文件号码</t>
+  </si>
+  <si>
+    <t>30 主管部门许可证号码</t>
+  </si>
+  <si>
+    <t>31 建筑施工及安装合同号码</t>
+  </si>
+  <si>
+    <t>32 组织机构占位号码</t>
+  </si>
+  <si>
+    <t>33 分支机构替代号码</t>
+  </si>
+  <si>
+    <t>34 SPV登记编码</t>
+  </si>
+  <si>
+    <t>99 其他</t>
+  </si>
+  <si>
+    <t>AFG 阿富汗</t>
+  </si>
+  <si>
+    <t>ALB 阿尔巴尼亚</t>
+  </si>
+  <si>
+    <t>DZA 阿尔及利亚</t>
+  </si>
+  <si>
+    <t>ASM 美属萨摩亚</t>
+  </si>
+  <si>
+    <t>AND 安道尔</t>
+  </si>
+  <si>
+    <t>AGO 安哥拉</t>
+  </si>
+  <si>
+    <t>AIA 安圭拉</t>
+  </si>
+  <si>
+    <t>ATA 南极洲</t>
+  </si>
+  <si>
+    <t>ATG 安提瓜和巴布达</t>
+  </si>
+  <si>
+    <t>ARG 阿根廷</t>
+  </si>
+  <si>
+    <t>ARM 亚美尼亚</t>
+  </si>
+  <si>
+    <t>ABW 阿鲁巴</t>
+  </si>
+  <si>
+    <t>AUS 澳大利亚</t>
+  </si>
+  <si>
+    <t>AUT 奥地利</t>
+  </si>
+  <si>
+    <t>AZE 阿塞拜疆</t>
+  </si>
+  <si>
+    <t>BHS 巴哈马</t>
+  </si>
+  <si>
+    <t>BHR 巴林</t>
+  </si>
+  <si>
+    <t>BGD 孟加拉国</t>
+  </si>
+  <si>
+    <t>BRB 巴巴多斯</t>
+  </si>
+  <si>
+    <t>BLR 白俄罗斯</t>
+  </si>
+  <si>
+    <t>BEL 比利时</t>
+  </si>
+  <si>
+    <t>BLZ 伯利兹</t>
+  </si>
+  <si>
+    <t>BEN 贝宁</t>
+  </si>
+  <si>
+    <t>BMU 百幕大</t>
+  </si>
+  <si>
+    <t>BTN 不丹</t>
+  </si>
+  <si>
+    <t>BOL 玻利维亚</t>
+  </si>
+  <si>
+    <t>BIH 波黑BIH</t>
+  </si>
+  <si>
+    <t>BWA 博茨瓦纳</t>
+  </si>
+  <si>
+    <t>BVT 布维岛</t>
+  </si>
+  <si>
+    <t>BRA 巴西</t>
+  </si>
+  <si>
+    <t>IOT 英属印度洋领土</t>
+  </si>
+  <si>
+    <t>BRN 文菜</t>
+  </si>
+  <si>
+    <t>BGR 保加利亚</t>
+  </si>
+  <si>
+    <t>BFA 布基纳法索</t>
+  </si>
+  <si>
+    <t>BDI 布隆迪</t>
+  </si>
+  <si>
+    <t>KHM 柬埔寨</t>
+  </si>
+  <si>
+    <t>CMR 喀麦隆</t>
+  </si>
+  <si>
+    <t>CAN 加拿大</t>
+  </si>
+  <si>
+    <t>CPV 佛得角</t>
+  </si>
+  <si>
+    <t>CYM 开曼群岛冷</t>
+  </si>
+  <si>
+    <t>CAF 中非</t>
+  </si>
+  <si>
+    <t>TCD 乍得</t>
+  </si>
+  <si>
+    <t>CHL 智利</t>
+  </si>
+  <si>
+    <t>CHN 中国</t>
+  </si>
+  <si>
+    <t>HKG 香港</t>
+  </si>
+  <si>
+    <t>MAC 澳门</t>
+  </si>
+  <si>
+    <t>TWN 台湾</t>
+  </si>
+  <si>
+    <t>CSR 圣诞岛</t>
+  </si>
+  <si>
+    <t>CCK 科科斯(基林) 群岛</t>
+  </si>
+  <si>
+    <t>COL 哥伦比亚</t>
+  </si>
+  <si>
+    <t>COM 科摩罗</t>
+  </si>
+  <si>
+    <t>COG 刚果(布)</t>
+  </si>
+  <si>
+    <t>COD 刚果(金)</t>
+  </si>
+  <si>
+    <t>COK 库克群岛</t>
+  </si>
+  <si>
+    <t>CRI 哥斯达黎加</t>
+  </si>
+  <si>
+    <t>CIV 科特迪瓦</t>
+  </si>
+  <si>
+    <t>HRV 克罗地亚</t>
+  </si>
+  <si>
+    <t>CUB 古巴</t>
+  </si>
+  <si>
+    <t>CYP 塞浦路斯</t>
+  </si>
+  <si>
+    <t>CZE 捷克</t>
+  </si>
+  <si>
+    <t>DNK 丹麦</t>
+  </si>
+  <si>
+    <t>DJI 吉布提</t>
+  </si>
+  <si>
+    <t>DMA 多米尼克</t>
+  </si>
+  <si>
+    <t>DOM 多米尼加共和国</t>
+  </si>
+  <si>
+    <t>TMP 东帝汶</t>
+  </si>
+  <si>
+    <t>ECU 厄瓜多尔</t>
+  </si>
+  <si>
+    <t>EGY 埃及</t>
+  </si>
+  <si>
+    <t>SLV 萨尔瓦多</t>
+  </si>
+  <si>
+    <t>GNQ 赤道几内亚</t>
+  </si>
+  <si>
+    <t>ERI 厄立特里亚</t>
+  </si>
+  <si>
+    <t>EST 爱沙尼亚</t>
+  </si>
+  <si>
+    <t>ETH 埃塞俄比亚</t>
+  </si>
+  <si>
+    <t>FLK 福克兰群岛(马尔维纳斯)</t>
+  </si>
+  <si>
+    <t>FRO 法罗群岛</t>
+  </si>
+  <si>
+    <t>FJI 斐济</t>
+  </si>
+  <si>
+    <t>FIN 芬兰</t>
+  </si>
+  <si>
+    <t>FRA 法国</t>
+  </si>
+  <si>
+    <t>GUF 法属圭亚那</t>
+  </si>
+  <si>
+    <t>PYF 法属波利尼西亚</t>
+  </si>
+  <si>
+    <t>ATF 法属南部领土</t>
+  </si>
+  <si>
+    <t>GAB 加蓬</t>
+  </si>
+  <si>
+    <t>GMB 冈比亚Gambia</t>
+  </si>
+  <si>
+    <t>GEO 格鲁吉亚</t>
+  </si>
+  <si>
+    <t>DEU 德国</t>
+  </si>
+  <si>
+    <t>GHA 加纳</t>
+  </si>
+  <si>
+    <t>GIB 直布罗陀</t>
+  </si>
+  <si>
+    <t>GRC 希腊</t>
+  </si>
+  <si>
+    <t>GRL 格陵兰</t>
+  </si>
+  <si>
+    <t>GRD 格林纳达</t>
+  </si>
+  <si>
+    <t>GLP 瓜德罗普</t>
+  </si>
+  <si>
+    <t>GUM 关岛</t>
+  </si>
+  <si>
+    <t>GTM 危地马拉</t>
+  </si>
+  <si>
+    <t>GIN 几内亚</t>
+  </si>
+  <si>
+    <t>GNB 几内亚比绍</t>
+  </si>
+  <si>
+    <t>GUY 圭亚那</t>
+  </si>
+  <si>
+    <t>HTI 海地</t>
+  </si>
+  <si>
+    <t>HMD 赫德岛和麦克唐纳岛</t>
+  </si>
+  <si>
+    <t>HND 洪都拉斯</t>
+  </si>
+  <si>
+    <t>HUN 匈牙利</t>
+  </si>
+  <si>
+    <t>ISL 冰岛</t>
+  </si>
+  <si>
+    <t>IND 印度</t>
+  </si>
+  <si>
+    <t>IDN 印度尼西亚</t>
+  </si>
+  <si>
+    <t>IRN 伊朗</t>
+  </si>
+  <si>
+    <t>IRQ 伊拉克</t>
+  </si>
+  <si>
+    <t>IRL 爱尔兰</t>
+  </si>
+  <si>
+    <t>ISR 以色列</t>
+  </si>
+  <si>
+    <t>ITA 意大利</t>
+  </si>
+  <si>
+    <t>JAM 牙买加</t>
+  </si>
+  <si>
+    <t>JPN 日本</t>
+  </si>
+  <si>
+    <t>JOR 约日</t>
+  </si>
+  <si>
+    <t>KAZ 哈萨克斯坦</t>
+  </si>
+  <si>
+    <t>KEN 肯尼迪</t>
+  </si>
+  <si>
+    <t>KIR 基里巴斯</t>
+  </si>
+  <si>
+    <t>PRK 朝鲜</t>
+  </si>
+  <si>
+    <t>KOR 韩国</t>
+  </si>
+  <si>
+    <t>KWT 科威特</t>
+  </si>
+  <si>
+    <t>KGZ 吉尔吉斯斯坦</t>
+  </si>
+  <si>
+    <t>LAO 老挝</t>
+  </si>
+  <si>
+    <t>LVA 拉脱维亚</t>
+  </si>
+  <si>
+    <t>LBN 黎巴嫩</t>
+  </si>
+  <si>
+    <t>LSO 莱索托</t>
+  </si>
+  <si>
+    <t>LBR 利比里亚</t>
+  </si>
+  <si>
+    <t>LBY 利比亚</t>
+  </si>
+  <si>
+    <t>LIE 列支敦士登</t>
+  </si>
+  <si>
+    <t>LTU 立陶宛</t>
+  </si>
+  <si>
+    <t>LUX 卢森堡</t>
+  </si>
+  <si>
+    <t>MKD 前南马其顿</t>
+  </si>
+  <si>
+    <t>MDG 马达加斯加</t>
+  </si>
+  <si>
+    <t>MWI 马拉维</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYS 马来西亚 </t>
+  </si>
+  <si>
+    <t>MDV 马尔代夫</t>
+  </si>
+  <si>
+    <t>MLI 马里</t>
+  </si>
+  <si>
+    <t>MLT 马耳他</t>
+  </si>
+  <si>
+    <t>MHL 马绍尔群岛</t>
+  </si>
+  <si>
+    <t>MTQ 马提尼克</t>
+  </si>
+  <si>
+    <t>MRT 毛里塔尼亚</t>
+  </si>
+  <si>
+    <t>MUS 毛里求斯</t>
+  </si>
+  <si>
+    <t>MYT 马约特</t>
+  </si>
+  <si>
+    <t>MEX 墨西哥</t>
+  </si>
+  <si>
+    <t>FSM 密克罗尼西亚联邦</t>
+  </si>
+  <si>
+    <t>MDA 摩尔多瓦</t>
+  </si>
+  <si>
+    <t>MCO 摩纳哥</t>
+  </si>
+  <si>
+    <t>MNG 蒙古</t>
+  </si>
+  <si>
+    <t>MSR 蒙特塞拉特</t>
+  </si>
+  <si>
+    <t>MAR 摩洛哥</t>
+  </si>
+  <si>
+    <t>MOZ 莫桑比克</t>
+  </si>
+  <si>
+    <t>MMR 缅甸</t>
+  </si>
+  <si>
+    <t>NAM 纳米比亚</t>
+  </si>
+  <si>
+    <t>NRU 瑙鲁</t>
+  </si>
+  <si>
+    <t>NPL 尼泊尔</t>
+  </si>
+  <si>
+    <t>NLD 荷兰</t>
+  </si>
+  <si>
+    <t>ANT 荷属安的列斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCL 新喀里多尼亚 </t>
+  </si>
+  <si>
+    <t>NZL 新西兰</t>
+  </si>
+  <si>
+    <t>NIC 尼加拉瓜</t>
+  </si>
+  <si>
+    <t>NER 尼日尔</t>
+  </si>
+  <si>
+    <t>NGA 尼日利亚</t>
+  </si>
+  <si>
+    <t>NIU 纽埃</t>
+  </si>
+  <si>
+    <t>NFK 诺福克岛</t>
+  </si>
+  <si>
+    <t>MNP 北马里亚纳</t>
+  </si>
+  <si>
+    <t>NOR 挪威</t>
+  </si>
+  <si>
+    <t>OMN 阿曼</t>
+  </si>
+  <si>
+    <t>PAK 巴基斯坦</t>
+  </si>
+  <si>
+    <t>PLW 帕劳</t>
+  </si>
+  <si>
+    <t>PST 巴勒斯坦</t>
+  </si>
+  <si>
+    <t>PAN 巴拿马</t>
+  </si>
+  <si>
+    <t>PNG 巴布亚新几内亚</t>
+  </si>
+  <si>
+    <t>PRY 巴拉圭</t>
+  </si>
+  <si>
+    <t>PER 秘鲁</t>
+  </si>
+  <si>
+    <t>PHL 菲律宾</t>
+  </si>
+  <si>
+    <t>PCN 皮特凯恩群岛</t>
+  </si>
+  <si>
+    <t>POL 波兰</t>
+  </si>
+  <si>
+    <t>PRT 葡葡牙</t>
+  </si>
+  <si>
+    <t>PRI 波多黎各</t>
+  </si>
+  <si>
+    <t>QAT 卡塔尔</t>
+  </si>
+  <si>
+    <t>REU 留尼汪</t>
+  </si>
+  <si>
+    <t>ROM 罗马尼亚</t>
+  </si>
+  <si>
+    <t>RUS 俄罗斯联邦</t>
+  </si>
+  <si>
+    <t>RWA 点旺达</t>
+  </si>
+  <si>
+    <t>SHN 圣赫勒拿</t>
+  </si>
+  <si>
+    <t>KNA 圣基茨和尼维斯</t>
+  </si>
+  <si>
+    <t>LCA 圣卢西亚</t>
+  </si>
+  <si>
+    <t>SPM 圣皮埃尔和密克隆</t>
+  </si>
+  <si>
+    <t>VCT 圣文森特和格林纳丁斯</t>
+  </si>
+  <si>
+    <t>WSM 萨摩亚</t>
+  </si>
+  <si>
+    <t>SMR 圣马力诺</t>
+  </si>
+  <si>
+    <t>STP 圣多美和普林西比</t>
+  </si>
+  <si>
+    <t>SAU 沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>SEN 基内加尔</t>
+  </si>
+  <si>
+    <t>SYC 塞舌尔</t>
+  </si>
+  <si>
+    <t>SLE 塞拉利昂</t>
+  </si>
+  <si>
+    <t>SGP 新加坡</t>
+  </si>
+  <si>
+    <t>SVK 斯洛伐克</t>
+  </si>
+  <si>
+    <t>SVN 斯洛文尼亚</t>
+  </si>
+  <si>
+    <t>SLB 所罗门群岛</t>
+  </si>
+  <si>
+    <t>SOM 索马里</t>
+  </si>
+  <si>
+    <t>ZAF 南非</t>
+  </si>
+  <si>
+    <t>SGS 南存治亚岛和南桑德韦奇岛</t>
+  </si>
+  <si>
+    <t>ESP 西班牙</t>
+  </si>
+  <si>
+    <t>LKA 斯里兰卡</t>
+  </si>
+  <si>
+    <t>SDN 苏丹</t>
+  </si>
+  <si>
+    <t>SUR 苏里南</t>
+  </si>
+  <si>
+    <t>SJM 斯瓦尔区群岛</t>
+  </si>
+  <si>
+    <t>SWZ 斯威士兰</t>
+  </si>
+  <si>
+    <t>SWE 瑞典</t>
+  </si>
+  <si>
+    <t>CHE 瑞士</t>
+  </si>
+  <si>
+    <t>SYR 叙利亚</t>
+  </si>
+  <si>
+    <t>TJK 塔吉克斯坦</t>
+  </si>
+  <si>
+    <t>TZA 坦桑尼亚</t>
+  </si>
+  <si>
+    <t>THA 泰国</t>
+  </si>
+  <si>
+    <t>TGO 多哥</t>
+  </si>
+  <si>
+    <t>TKL 托克劳</t>
+  </si>
+  <si>
+    <t>TON 汤加</t>
+  </si>
+  <si>
+    <t>TTO 特立尼达和多巴哥</t>
+  </si>
+  <si>
+    <t>TUN 突尼斯</t>
+  </si>
+  <si>
+    <t>TUR 土耳其</t>
+  </si>
+  <si>
+    <t>TKM 土库曼斯坦</t>
+  </si>
+  <si>
+    <t>TCA 特克斯科斯群岛</t>
+  </si>
+  <si>
+    <t>TUV 图瓦卢</t>
+  </si>
+  <si>
+    <t>UGA 乌干达</t>
+  </si>
+  <si>
+    <t>UKR 乌克兰</t>
+  </si>
+  <si>
+    <t>ARE 阿联酋</t>
+  </si>
+  <si>
+    <t>GBR 英国</t>
+  </si>
+  <si>
+    <t>USA 美国</t>
+  </si>
+  <si>
+    <t>UMI 美国本土外小岛屿</t>
+  </si>
+  <si>
+    <t>URY 乌拉圭</t>
+  </si>
+  <si>
+    <t>UZB 乌兹别克斯坦</t>
+  </si>
+  <si>
+    <t>VUT 瓦努阿图</t>
+  </si>
+  <si>
+    <t>VAT 梵蒂冈</t>
+  </si>
+  <si>
+    <t>VEN 委内瑞拉</t>
+  </si>
+  <si>
+    <t>VNM 越南</t>
+  </si>
+  <si>
+    <t>VGB 英属维尔京群岛</t>
+  </si>
+  <si>
+    <t>VIR 美属维尔京群岛</t>
+  </si>
+  <si>
+    <t>WLF 瓦利斯和富图纳</t>
+  </si>
+  <si>
+    <t>ESH 西撒哈拉</t>
+  </si>
+  <si>
+    <t>YEM 也门</t>
+  </si>
+  <si>
+    <t>YUG 南斯拉夫</t>
+  </si>
+  <si>
+    <t>ZMB 赞比亚</t>
+  </si>
+  <si>
+    <t>ZWE 津巴布韦</t>
+  </si>
+</sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="13">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF373737"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="6">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF373737"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF373737"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF373737"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF373737"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+  </cellXfs>
+  <cellStyles count="3">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF373737"/>
+      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FF8DB4E2"/>
+      <color rgb="FF000000"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office 2007-2010">
@@ -280,9 +1602,2673 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
-<file path=theme/theme/themeManager.xml><?xml version="1.0" encoding="utf-8"?>
-<a:themeManager xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AA34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="10" customWidth="1"/>
+    <col min="5" max="5" width="27.625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.25" style="10" customWidth="1"/>
+    <col min="9" max="9" width="19" style="10" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="31.625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="24.75" style="10" customWidth="1"/>
+    <col min="13" max="13" width="22.75" style="10" customWidth="1"/>
+    <col min="14" max="14" width="23.25" style="10" customWidth="1"/>
+    <col min="15" max="15" width="23.375" style="10" customWidth="1"/>
+    <col min="16" max="16" width="23.25" style="10" customWidth="1"/>
+    <col min="17" max="17" width="8.875" style="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" style="10" customWidth="1"/>
+    <col min="19" max="19" width="12.75" style="10" customWidth="1"/>
+    <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
+    <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
+    <col min="23" max="24" width="18.25" style="11" customWidth="1"/>
+    <col min="25" max="25" width="14.125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="21" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="23"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="23"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+    </row>
+    <row r="8" spans="1:27">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+    </row>
+    <row r="9" spans="1:27">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+    </row>
+    <row r="10" spans="1:27">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+    </row>
+    <row r="15" spans="1:27">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+    </row>
+    <row r="16" spans="1:27">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="23"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+    </row>
+    <row r="21" spans="1:27">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="23"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="23"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="23"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="23"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="23"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="23"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="21"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="23"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6"/>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="21"/>
+      <c r="T30" s="21"/>
+      <c r="U30" s="21"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="23"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="23"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="21"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="23"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+    </row>
+    <row r="33" spans="1:27">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="23"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+    </row>
+    <row r="34" spans="1:27">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21"/>
+      <c r="U34" s="21"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="23"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D65536">
+      <formula1>"01 是,02 否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576">
+      <formula1>"01 境内,02 境外"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576">
+      <formula1>"00 居民身份证,01 临时居民身份证,02 户口簿,10 军官证,11 警官证,12 文职干部证,13 士兵证,14 军事院校学员证,15 离休干部荣誉证,16 军官退休证,17 文职干部退休证,20 中华人民共和国护照,21 外国护照,22 港澳往来内地通行证,23 台湾往来内地通行证,24 外国人永久居留证,99 其他,"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576">
+      <formula1>"26 其他非法人组织,25 合伙企业,24 个人独资企业,23 私募基金,22 社会保障类基金,21 保险资产管理计划,20 期货资产管理计划,19 基金资产管理计划,18 券商资产管理计划,17 信托产品,16 其他法人机构,15 机关,14 社会服务机构,13 基金会,12 社会团体,11 事业单位,10 其他金融机构,09 期货公司,08 保险公司,07 基金公司,06 证券公司,05 信托公司,04 银行,03 私人银行客户,02 高净值客户,01 普通个人"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
+      <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1:Q1048576">
+      <formula1>"01 男,02 女"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$73:$A$311</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A311"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="100.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="33.75" customHeight="1">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:1" ht="38.25" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="33" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="33" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="9" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="9" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="9" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="9" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20130" windowHeight="7710"/>
+    <workbookView windowWidth="19815" windowHeight="7860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息维护模板" sheetId="1" r:id="rId1"/>
@@ -225,7 +220,7 @@
     <t>C10868 江苏银行股份有限公司</t>
   </si>
   <si>
-    <t>99999 其他</t>
+    <t>999999 其他</t>
   </si>
   <si>
     <t>机构证件类别枚举值</t>
@@ -1056,8 +1051,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,6 +1125,142 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
@@ -1135,21 +1272,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1158,12 +1282,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1238,20 +1548,259 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1287,35 +1836,78 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="FF373737"/>
-      <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
-      <color rgb="FF8DB4E2"/>
-      <color rgb="FF000000"/>
+      <color rgb="00373737"/>
+      <color rgb="000000FF"/>
+      <color rgb="00FF0000"/>
+      <color rgb="008DB4E2"/>
+      <color rgb="00000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1602,12 +2194,12 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -1637,7 +2229,7 @@
     <col min="25" max="25" width="14.125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" customHeight="1">
+    <row r="1" ht="21" customHeight="1" spans="1:27">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2674,66 +3266,58 @@
       <c r="AA34" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D65536">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"01 境内,02 境外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+      <formula1>填写说明!$A$73:$A$311</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+      <formula1>"26 其他非法人组织,25 合伙企业,24 个人独资企业,23 私募基金,22 社会保障类基金,21 保险资产管理计划,20 期货资产管理计划,19 基金资产管理计划,18 券商资产管理计划,17 信托产品,16 其他法人机构,15 机关,14 社会服务机构,13 基金会,12 社会团体,11 事业单位,10 其他金融机构,09 期货公司,08 保险公司,07 基金公司,06 证券公司,05 信托公司,04 银行,03 私人银行客户,02 高净值客户,01 普通个人"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"00 居民身份证,01 临时居民身份证,02 户口簿,10 军官证,11 警官证,12 文职干部证,13 士兵证,14 军事院校学员证,15 离休干部荣誉证,16 军官退休证,17 文职干部退休证,20 中华人民共和国护照,21 外国护照,22 港澳往来内地通行证,23 台湾往来内地通行证,24 外国人永久居留证,99 其他,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576">
-      <formula1>"26 其他非法人组织,25 合伙企业,24 个人独资企业,23 私募基金,22 社会保障类基金,21 保险资产管理计划,20 期货资产管理计划,19 基金资产管理计划,18 券商资产管理计划,17 信托产品,16 其他法人机构,15 机关,14 社会服务机构,13 基金会,12 社会团体,11 事业单位,10 其他金融机构,09 期货公司,08 保险公司,07 基金公司,06 证券公司,05 信托公司,04 银行,03 私人银行客户,02 高净值客户,01 普通个人"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576">
+      <formula1>"01 男,02 女"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R$1:R$1048576">
       <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1:Q1048576">
-      <formula1>"01 男,02 女"</formula1>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$73:$A$311</xm:f>
-          </x14:formula1>
-          <xm:sqref>H1:H1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A311"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="100.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="33.75" customHeight="1">
+    <row r="1" ht="33.75" customHeight="1" spans="1:1">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" ht="38.25" customHeight="1">
+    <row r="2" ht="38.25" customHeight="1" spans="1:1">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="33" customHeight="1">
+    <row r="3" ht="33" customHeight="1" spans="1:1">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="33" customHeight="1">
+    <row r="4" ht="33" customHeight="1" spans="1:1">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -4267,8 +4851,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7860" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息维护模板" sheetId="1" r:id="rId1"/>
@@ -15,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="333">
   <si>
     <t>登记银行代码*</t>
   </si>
@@ -87,9 +92,6 @@
   </si>
   <si>
     <t>接入检查结果</t>
-  </si>
-  <si>
-    <t>中债反馈消息</t>
   </si>
   <si>
     <r>
@@ -1047,18 +1049,20 @@
   <si>
     <t>ZWE 津巴布韦</t>
   </si>
+  <si>
+    <t>中债反馈消息</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者分类*</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1125,139 +1129,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1272,8 +1147,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1282,198 +1163,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1548,259 +1243,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1836,78 +1292,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="2"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="00373737"/>
-      <color rgb="000000FF"/>
-      <color rgb="00FF0000"/>
-      <color rgb="008DB4E2"/>
-      <color rgb="00000000"/>
+      <color rgb="FF373737"/>
+      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FF8DB4E2"/>
+      <color rgb="FF000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2194,12 +1607,12 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -2227,9 +1640,10 @@
     <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
     <col min="23" max="24" width="18.25" style="11" customWidth="1"/>
     <col min="25" max="25" width="14.125"/>
+    <col min="26" max="26" width="19" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:27">
+    <row r="1" spans="1:27" ht="21" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2303,9 +1717,11 @@
         <v>23</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="6"/>
+        <v>331</v>
+      </c>
+      <c r="Z1" s="22" t="s">
+        <v>332</v>
+      </c>
       <c r="AA1" s="6"/>
     </row>
     <row r="2" spans="1:27">
@@ -2334,7 +1750,7 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="23"/>
-      <c r="Z2" s="6"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="6"/>
     </row>
     <row r="3" spans="1:27">
@@ -2363,7 +1779,7 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="23"/>
-      <c r="Z3" s="6"/>
+      <c r="Z3" s="13"/>
       <c r="AA3" s="6"/>
     </row>
     <row r="4" spans="1:27">
@@ -2392,7 +1808,7 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="23"/>
-      <c r="Z4" s="6"/>
+      <c r="Z4" s="13"/>
       <c r="AA4" s="6"/>
     </row>
     <row r="5" spans="1:27">
@@ -2421,7 +1837,7 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="23"/>
-      <c r="Z5" s="6"/>
+      <c r="Z5" s="13"/>
       <c r="AA5" s="6"/>
     </row>
     <row r="6" spans="1:27">
@@ -2450,7 +1866,7 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="6"/>
+      <c r="Z6" s="13"/>
       <c r="AA6" s="6"/>
     </row>
     <row r="7" spans="1:27">
@@ -2479,7 +1895,7 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="23"/>
-      <c r="Z7" s="6"/>
+      <c r="Z7" s="13"/>
       <c r="AA7" s="6"/>
     </row>
     <row r="8" spans="1:27">
@@ -2508,7 +1924,7 @@
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="23"/>
-      <c r="Z8" s="6"/>
+      <c r="Z8" s="13"/>
       <c r="AA8" s="6"/>
     </row>
     <row r="9" spans="1:27">
@@ -2537,7 +1953,7 @@
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="23"/>
-      <c r="Z9" s="6"/>
+      <c r="Z9" s="13"/>
       <c r="AA9" s="6"/>
     </row>
     <row r="10" spans="1:27">
@@ -2566,7 +1982,7 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="23"/>
-      <c r="Z10" s="6"/>
+      <c r="Z10" s="13"/>
       <c r="AA10" s="6"/>
     </row>
     <row r="11" spans="1:27">
@@ -2595,7 +2011,7 @@
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="23"/>
-      <c r="Z11" s="6"/>
+      <c r="Z11" s="13"/>
       <c r="AA11" s="6"/>
     </row>
     <row r="12" spans="1:27">
@@ -2624,7 +2040,7 @@
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="6"/>
+      <c r="Z12" s="13"/>
       <c r="AA12" s="6"/>
     </row>
     <row r="13" spans="1:27">
@@ -2653,7 +2069,7 @@
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="23"/>
-      <c r="Z13" s="6"/>
+      <c r="Z13" s="13"/>
       <c r="AA13" s="6"/>
     </row>
     <row r="14" spans="1:27">
@@ -2682,7 +2098,7 @@
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="23"/>
-      <c r="Z14" s="6"/>
+      <c r="Z14" s="13"/>
       <c r="AA14" s="6"/>
     </row>
     <row r="15" spans="1:27">
@@ -2711,7 +2127,7 @@
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="23"/>
-      <c r="Z15" s="6"/>
+      <c r="Z15" s="13"/>
       <c r="AA15" s="6"/>
     </row>
     <row r="16" spans="1:27">
@@ -2740,7 +2156,7 @@
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="23"/>
-      <c r="Z16" s="6"/>
+      <c r="Z16" s="13"/>
       <c r="AA16" s="6"/>
     </row>
     <row r="17" spans="1:27">
@@ -2769,7 +2185,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="23"/>
-      <c r="Z17" s="6"/>
+      <c r="Z17" s="13"/>
       <c r="AA17" s="6"/>
     </row>
     <row r="18" spans="1:27">
@@ -2798,7 +2214,7 @@
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="23"/>
-      <c r="Z18" s="6"/>
+      <c r="Z18" s="13"/>
       <c r="AA18" s="6"/>
     </row>
     <row r="19" spans="1:27">
@@ -2827,7 +2243,7 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="23"/>
-      <c r="Z19" s="6"/>
+      <c r="Z19" s="13"/>
       <c r="AA19" s="6"/>
     </row>
     <row r="20" spans="1:27">
@@ -2856,7 +2272,7 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="6"/>
+      <c r="Z20" s="13"/>
       <c r="AA20" s="6"/>
     </row>
     <row r="21" spans="1:27">
@@ -2885,7 +2301,7 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="23"/>
-      <c r="Z21" s="6"/>
+      <c r="Z21" s="13"/>
       <c r="AA21" s="6"/>
     </row>
     <row r="22" spans="1:27">
@@ -2914,7 +2330,7 @@
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="23"/>
-      <c r="Z22" s="6"/>
+      <c r="Z22" s="13"/>
       <c r="AA22" s="6"/>
     </row>
     <row r="23" spans="1:27">
@@ -2943,7 +2359,7 @@
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="23"/>
-      <c r="Z23" s="6"/>
+      <c r="Z23" s="13"/>
       <c r="AA23" s="6"/>
     </row>
     <row r="24" spans="1:27">
@@ -2972,7 +2388,7 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="23"/>
-      <c r="Z24" s="6"/>
+      <c r="Z24" s="13"/>
       <c r="AA24" s="6"/>
     </row>
     <row r="25" spans="1:27">
@@ -3001,7 +2417,7 @@
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="23"/>
-      <c r="Z25" s="6"/>
+      <c r="Z25" s="13"/>
       <c r="AA25" s="6"/>
     </row>
     <row r="26" spans="1:27">
@@ -3030,7 +2446,7 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="23"/>
-      <c r="Z26" s="6"/>
+      <c r="Z26" s="13"/>
       <c r="AA26" s="6"/>
     </row>
     <row r="27" spans="1:27">
@@ -3059,7 +2475,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="23"/>
-      <c r="Z27" s="6"/>
+      <c r="Z27" s="13"/>
       <c r="AA27" s="6"/>
     </row>
     <row r="28" spans="1:27">
@@ -3088,7 +2504,7 @@
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="23"/>
-      <c r="Z28" s="6"/>
+      <c r="Z28" s="13"/>
       <c r="AA28" s="6"/>
     </row>
     <row r="29" spans="1:27">
@@ -3117,7 +2533,7 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="23"/>
-      <c r="Z29" s="6"/>
+      <c r="Z29" s="13"/>
       <c r="AA29" s="6"/>
     </row>
     <row r="30" spans="1:27">
@@ -3146,7 +2562,7 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="23"/>
-      <c r="Z30" s="6"/>
+      <c r="Z30" s="13"/>
       <c r="AA30" s="6"/>
     </row>
     <row r="31" spans="1:27">
@@ -3175,7 +2591,7 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="23"/>
-      <c r="Z31" s="6"/>
+      <c r="Z31" s="13"/>
       <c r="AA31" s="6"/>
     </row>
     <row r="32" spans="1:27">
@@ -3204,7 +2620,7 @@
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="23"/>
-      <c r="Z32" s="6"/>
+      <c r="Z32" s="13"/>
       <c r="AA32" s="6"/>
     </row>
     <row r="33" spans="1:27">
@@ -3233,7 +2649,7 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33" s="23"/>
-      <c r="Z33" s="6"/>
+      <c r="Z33" s="13"/>
       <c r="AA33" s="6"/>
     </row>
     <row r="34" spans="1:27">
@@ -3262,209 +2678,220 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="23"/>
-      <c r="Z34" s="6"/>
+      <c r="Z34" s="13"/>
       <c r="AA34" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D65536">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576">
       <formula1>"01 境内,02 境外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
-      <formula1>填写说明!$A$73:$A$311</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576">
       <formula1>"26 其他非法人组织,25 合伙企业,24 个人独资企业,23 私募基金,22 社会保障类基金,21 保险资产管理计划,20 期货资产管理计划,19 基金资产管理计划,18 券商资产管理计划,17 信托产品,16 其他法人机构,15 机关,14 社会服务机构,13 基金会,12 社会团体,11 事业单位,10 其他金融机构,09 期货公司,08 保险公司,07 基金公司,06 证券公司,05 信托公司,04 银行,03 私人银行客户,02 高净值客户,01 普通个人"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576">
       <formula1>"00 居民身份证,01 临时居民身份证,02 户口簿,10 军官证,11 警官证,12 文职干部证,13 士兵证,14 军事院校学员证,15 离休干部荣誉证,16 军官退休证,17 文职干部退休证,20 中华人民共和国护照,21 外国护照,22 港澳往来内地通行证,23 台湾往来内地通行证,24 外国人永久居留证,99 其他,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q$1:Q$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1:Q1048576">
       <formula1>"01 男,02 女"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R$1:R$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
       <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+      <formula1>"02 合格投资者,01 不特定社会公众"</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$73:$A$311</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A311"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="100.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1" spans="1:1">
+    <row r="1" spans="1:1" ht="33.75" customHeight="1">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" ht="38.25" customHeight="1" spans="1:1">
+    <row r="2" spans="1:1" ht="38.25" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="33" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" ht="33" customHeight="1" spans="1:1">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:1" ht="33" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="4" ht="33" customHeight="1" spans="1:1">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -3472,182 +2899,182 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -3657,1202 +3084,1202 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -99,6 +99,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
@@ -108,6 +109,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“选择性粘贴”</t>
@@ -117,6 +119,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>并只</t>
@@ -126,6 +129,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“粘贴数值”</t>
@@ -1075,6 +1079,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1082,6 +1087,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1090,12 +1096,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1103,6 +1111,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1110,6 +1119,7 @@
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1117,6 +1127,7 @@
       <sz val="11"/>
       <color rgb="FF373737"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1125,6 +1136,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1132,6 +1144,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1139,17 +1152,20 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1613,7 +1629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
@@ -1638,12 +1654,12 @@
     <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
     <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
     <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
-    <col min="23" max="24" width="18.25" style="11" customWidth="1"/>
-    <col min="25" max="25" width="14.125"/>
-    <col min="26" max="26" width="19" style="10" customWidth="1"/>
+    <col min="23" max="23" width="19" style="10" customWidth="1"/>
+    <col min="24" max="25" width="18.25" style="11" customWidth="1"/>
+    <col min="26" max="26" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" customHeight="1">
+    <row r="1" spans="1:26" ht="21" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1710,21 +1726,20 @@
       <c r="V1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="X1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="Z1" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="AA1" s="6"/>
-    </row>
-    <row r="2" spans="1:27">
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="13"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1749,11 +1764,10 @@
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="6"/>
-    </row>
-    <row r="3" spans="1:27">
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="23"/>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1778,11 +1792,10 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="6"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="23"/>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1807,11 +1820,10 @@
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="6"/>
-    </row>
-    <row r="5" spans="1:27">
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="23"/>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1836,11 +1848,10 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="6"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="23"/>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -1865,11 +1876,10 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="6"/>
-    </row>
-    <row r="7" spans="1:27">
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="23"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1894,11 +1904,10 @@
       <c r="V7" s="13"/>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="6"/>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="23"/>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1923,11 +1932,10 @@
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="6"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="23"/>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1952,11 +1960,10 @@
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="6"/>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="23"/>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1981,11 +1988,10 @@
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="6"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="23"/>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2010,11 +2016,10 @@
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="6"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="23"/>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2039,11 +2044,10 @@
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="6"/>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="23"/>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2068,11 +2072,10 @@
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="6"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="23"/>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2097,11 +2100,10 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="6"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="23"/>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2126,11 +2128,10 @@
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="6"/>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="23"/>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2155,11 +2156,10 @@
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="6"/>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="23"/>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2184,11 +2184,10 @@
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="6"/>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="23"/>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2213,11 +2212,10 @@
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="6"/>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="23"/>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2242,11 +2240,10 @@
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="6"/>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="23"/>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2271,11 +2268,10 @@
       <c r="V20" s="13"/>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="6"/>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="23"/>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2300,11 +2296,10 @@
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="6"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="23"/>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2329,11 +2324,10 @@
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="13"/>
-      <c r="AA22" s="6"/>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="23"/>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2358,11 +2352,10 @@
       <c r="V23" s="13"/>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="6"/>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="23"/>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2387,11 +2380,10 @@
       <c r="V24" s="13"/>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="6"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="23"/>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -2416,11 +2408,10 @@
       <c r="V25" s="13"/>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="6"/>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="23"/>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2445,11 +2436,10 @@
       <c r="V26" s="13"/>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="6"/>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="23"/>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -2474,11 +2464,10 @@
       <c r="V27" s="13"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="6"/>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="23"/>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2503,11 +2492,10 @@
       <c r="V28" s="13"/>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="6"/>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="23"/>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2532,11 +2520,10 @@
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="6"/>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="23"/>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2561,11 +2548,10 @@
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="13"/>
-      <c r="AA30" s="6"/>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="23"/>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2590,11 +2576,10 @@
       <c r="V31" s="13"/>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="13"/>
-      <c r="AA31" s="6"/>
-    </row>
-    <row r="32" spans="1:27">
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="23"/>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2619,11 +2604,10 @@
       <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="13"/>
-      <c r="AA32" s="6"/>
-    </row>
-    <row r="33" spans="1:27">
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="23"/>
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2648,11 +2632,10 @@
       <c r="V33" s="13"/>
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="13"/>
-      <c r="AA33" s="6"/>
-    </row>
-    <row r="34" spans="1:27">
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="23"/>
+    </row>
+    <row r="34" spans="1:26">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2677,9 +2660,8 @@
       <c r="V34" s="13"/>
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="13"/>
-      <c r="AA34" s="6"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -2702,7 +2684,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
       <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
       <formula1>"02 合格投资者,01 不特定社会公众"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\3.0.1\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息维护模板" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="375">
   <si>
     <t>登记银行代码*</t>
   </si>
@@ -1061,12 +1061,140 @@
     <t>投资者分类*</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
+  <si>
+    <t>110000 北京市</t>
+  </si>
+  <si>
+    <t>120000 天津市</t>
+  </si>
+  <si>
+    <t>130000 河北省</t>
+  </si>
+  <si>
+    <t>140000 山西省</t>
+  </si>
+  <si>
+    <t>150000 内蒙古自治区</t>
+  </si>
+  <si>
+    <t>210000 辽宁省</t>
+  </si>
+  <si>
+    <t>210200 大连市</t>
+  </si>
+  <si>
+    <t>220000 吉林省</t>
+  </si>
+  <si>
+    <t>230000 黑龙江省</t>
+  </si>
+  <si>
+    <t>310000 上海市</t>
+  </si>
+  <si>
+    <t>320000 江苏省</t>
+  </si>
+  <si>
+    <t>330000 浙江省</t>
+  </si>
+  <si>
+    <t>330200 宁波市</t>
+  </si>
+  <si>
+    <t>340000 安徽省</t>
+  </si>
+  <si>
+    <t>350000 福建省</t>
+  </si>
+  <si>
+    <t>350200 厦门市</t>
+  </si>
+  <si>
+    <t>360000 江西省</t>
+  </si>
+  <si>
+    <t>370000 山东省</t>
+  </si>
+  <si>
+    <t>370200 青岛市</t>
+  </si>
+  <si>
+    <t>410000 河南省</t>
+  </si>
+  <si>
+    <t>420000 湖北省</t>
+  </si>
+  <si>
+    <t>430000 湖南省</t>
+  </si>
+  <si>
+    <t>440000 广东省</t>
+  </si>
+  <si>
+    <t>440300 深圳市</t>
+  </si>
+  <si>
+    <t>450000 广西壮族自治区</t>
+  </si>
+  <si>
+    <t>460000 海南省</t>
+  </si>
+  <si>
+    <t>500000 重庆市</t>
+  </si>
+  <si>
+    <t>510000 四川省</t>
+  </si>
+  <si>
+    <t>520000 贵州省</t>
+  </si>
+  <si>
+    <t>530000 云南省</t>
+  </si>
+  <si>
+    <t>540000 西藏自治区</t>
+  </si>
+  <si>
+    <t>610000 陕西省</t>
+  </si>
+  <si>
+    <t>620000 甘肃省</t>
+  </si>
+  <si>
+    <t>630000 青海省</t>
+  </si>
+  <si>
+    <t>640000 宁夏回族自治区</t>
+  </si>
+  <si>
+    <t>650000 新疆维吾尔自治区</t>
+  </si>
+  <si>
+    <t>710000 台湾</t>
+  </si>
+  <si>
+    <t>810000 香港</t>
+  </si>
+  <si>
+    <t>820000 澳门</t>
+  </si>
+  <si>
+    <t>900000 其他国家或地区</t>
+  </si>
+  <si>
+    <t>中债销售区域</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号开户所在地</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1164,6 +1292,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1267,7 +1404,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1314,6 +1451,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1629,37 +1769,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AA34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
-    <col min="4" max="4" width="23.25" style="10" customWidth="1"/>
-    <col min="5" max="5" width="27.625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="19.625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.25" style="10" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="23.26953125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" style="10" customWidth="1"/>
     <col min="9" max="9" width="19" style="10" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="31.625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="24.75" style="10" customWidth="1"/>
-    <col min="13" max="13" width="22.75" style="10" customWidth="1"/>
-    <col min="14" max="14" width="23.25" style="10" customWidth="1"/>
-    <col min="15" max="15" width="23.375" style="10" customWidth="1"/>
-    <col min="16" max="16" width="23.25" style="10" customWidth="1"/>
-    <col min="17" max="17" width="8.875" style="10" customWidth="1"/>
-    <col min="18" max="18" width="10.875" style="10" customWidth="1"/>
-    <col min="19" max="19" width="12.75" style="10" customWidth="1"/>
-    <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
-    <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
-    <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
-    <col min="23" max="23" width="19" style="10" customWidth="1"/>
-    <col min="24" max="25" width="18.25" style="11" customWidth="1"/>
-    <col min="26" max="26" width="21.75" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" style="10" customWidth="1"/>
+    <col min="11" max="11" width="31.6328125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="24.7265625" style="10" customWidth="1"/>
+    <col min="13" max="13" width="22.7265625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="23.26953125" style="10" customWidth="1"/>
+    <col min="15" max="15" width="23.36328125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="23.26953125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="8.90625" style="10" customWidth="1"/>
+    <col min="18" max="18" width="10.90625" style="10" customWidth="1"/>
+    <col min="19" max="19" width="12.7265625" style="10" customWidth="1"/>
+    <col min="20" max="20" width="13.26953125" style="10" customWidth="1"/>
+    <col min="21" max="21" width="16.36328125" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12.453125" style="11" customWidth="1"/>
+    <col min="23" max="24" width="19" style="10" customWidth="1"/>
+    <col min="25" max="26" width="18.26953125" style="11" customWidth="1"/>
+    <col min="27" max="27" width="21.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21" customHeight="1">
+    <row r="1" spans="1:27" ht="21" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1729,17 +1869,20 @@
       <c r="W1" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="Y1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="13"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1765,9 +1908,10 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
-      <c r="Z2" s="23"/>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="23"/>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1793,9 +1937,10 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
-      <c r="Z3" s="23"/>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="23"/>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1821,9 +1966,10 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
-      <c r="Z4" s="23"/>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="23"/>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1849,9 +1995,10 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
-      <c r="Z5" s="23"/>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="23"/>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -1877,9 +2024,10 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="23"/>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="23"/>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1905,9 +2053,10 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
-      <c r="Z7" s="23"/>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="23"/>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1933,9 +2082,10 @@
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
-      <c r="Z8" s="23"/>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="23"/>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1961,9 +2111,10 @@
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
-      <c r="Z9" s="23"/>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="23"/>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1989,9 +2140,10 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
-      <c r="Z10" s="23"/>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="23"/>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2017,9 +2169,10 @@
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
-      <c r="Z11" s="23"/>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="23"/>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2045,9 +2198,10 @@
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="23"/>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="23"/>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2073,9 +2227,10 @@
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
-      <c r="Z13" s="23"/>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="23"/>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2101,9 +2256,10 @@
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
-      <c r="Z14" s="23"/>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="23"/>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2129,9 +2285,10 @@
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
-      <c r="Z15" s="23"/>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="23"/>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2157,9 +2314,10 @@
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
-      <c r="Z16" s="23"/>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="23"/>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2185,9 +2343,10 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
-      <c r="Z17" s="23"/>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="23"/>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2213,9 +2372,10 @@
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
-      <c r="Z18" s="23"/>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="23"/>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2241,9 +2401,10 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
-      <c r="Z19" s="23"/>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="23"/>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2269,9 +2430,10 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
-      <c r="Z20" s="23"/>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="23"/>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2297,9 +2459,10 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
-      <c r="Z21" s="23"/>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="23"/>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2325,9 +2488,10 @@
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
-      <c r="Z22" s="23"/>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="23"/>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2353,9 +2517,10 @@
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
-      <c r="Z23" s="23"/>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="23"/>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2381,9 +2546,10 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
-      <c r="Z24" s="23"/>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="23"/>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -2409,9 +2575,10 @@
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
-      <c r="Z25" s="23"/>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="23"/>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2437,9 +2604,10 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
-      <c r="Z26" s="23"/>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="23"/>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -2465,9 +2633,10 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
-      <c r="Z27" s="23"/>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="23"/>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2493,9 +2662,10 @@
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
-      <c r="Z28" s="23"/>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="23"/>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2521,9 +2691,10 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
-      <c r="Z29" s="23"/>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="23"/>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2549,9 +2720,10 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
-      <c r="Z30" s="23"/>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="23"/>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2577,9 +2749,10 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
-      <c r="Z31" s="23"/>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="23"/>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2605,9 +2778,10 @@
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
-      <c r="Z32" s="23"/>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="23"/>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2633,9 +2807,10 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
-      <c r="Z33" s="23"/>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="23"/>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2661,7 +2836,8 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
-      <c r="Z34" s="23"/>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -2692,12 +2868,18 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$73:$A$311</xm:f>
           </x14:formula1>
           <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$315:$A$354</xm:f>
+          </x14:formula1>
+          <xm:sqref>X1:X1048576 X1</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2707,10 +2889,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A311"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:A354"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="100.75" customWidth="1"/>
+    <col min="1" max="1" width="100.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="33.75" customHeight="1">
@@ -4259,9 +4441,214 @@
         <v>330</v>
       </c>
     </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="24" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" t="s">
+        <v>372</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="374">
   <si>
     <t>登记银行代码*</t>
   </si>
@@ -1183,10 +1183,6 @@
   </si>
   <si>
     <t>中债销售区域</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>账号开户所在地</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -1769,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14.90625" style="10" customWidth="1"/>
@@ -1794,12 +1790,12 @@
     <col min="20" max="20" width="13.26953125" style="10" customWidth="1"/>
     <col min="21" max="21" width="16.36328125" style="10" customWidth="1"/>
     <col min="22" max="22" width="12.453125" style="11" customWidth="1"/>
-    <col min="23" max="24" width="19" style="10" customWidth="1"/>
-    <col min="25" max="26" width="18.26953125" style="11" customWidth="1"/>
-    <col min="27" max="27" width="21.7265625" customWidth="1"/>
+    <col min="23" max="23" width="19" style="10" customWidth="1"/>
+    <col min="24" max="25" width="18.26953125" style="11" customWidth="1"/>
+    <col min="26" max="26" width="21.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" customHeight="1">
+    <row r="1" spans="1:26" ht="21" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1869,20 +1865,17 @@
       <c r="W1" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="X1" s="22" t="s">
-        <v>374</v>
+      <c r="X1" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:26">
       <c r="A2" s="13"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1908,10 +1901,9 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="23"/>
-    </row>
-    <row r="3" spans="1:27">
+      <c r="Z2" s="23"/>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1937,10 +1929,9 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="23"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="Z3" s="23"/>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1966,10 +1957,9 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="23"/>
-    </row>
-    <row r="5" spans="1:27">
+      <c r="Z4" s="23"/>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1995,10 +1985,9 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="23"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="Z5" s="23"/>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -2024,10 +2013,9 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="23"/>
-    </row>
-    <row r="7" spans="1:27">
+      <c r="Z6" s="23"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -2053,10 +2041,9 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="23"/>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="Z7" s="23"/>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2082,10 +2069,9 @@
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="23"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="Z8" s="23"/>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2111,10 +2097,9 @@
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="23"/>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="Z9" s="23"/>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2140,10 +2125,9 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="23"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="Z10" s="23"/>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2169,10 +2153,9 @@
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="23"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="Z11" s="23"/>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2198,10 +2181,9 @@
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="23"/>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="Z12" s="23"/>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2227,10 +2209,9 @@
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="23"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="Z13" s="23"/>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2256,10 +2237,9 @@
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="23"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="Z14" s="23"/>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2285,10 +2265,9 @@
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="23"/>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="Z15" s="23"/>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2314,10 +2293,9 @@
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="23"/>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="Z16" s="23"/>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2343,10 +2321,9 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="23"/>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="Z17" s="23"/>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2372,10 +2349,9 @@
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="23"/>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="Z18" s="23"/>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2401,10 +2377,9 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="23"/>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="Z19" s="23"/>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2430,10 +2405,9 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="23"/>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="Z20" s="23"/>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2459,10 +2433,9 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="23"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="Z21" s="23"/>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2488,10 +2461,9 @@
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
-      <c r="Z22" s="13"/>
-      <c r="AA22" s="23"/>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="Z22" s="23"/>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2517,10 +2489,9 @@
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="23"/>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="Z23" s="23"/>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2546,10 +2517,9 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="23"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="Z24" s="23"/>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -2575,10 +2545,9 @@
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="23"/>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="Z25" s="23"/>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2604,10 +2573,9 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="23"/>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="Z26" s="23"/>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -2633,10 +2601,9 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="23"/>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="Z27" s="23"/>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2662,10 +2629,9 @@
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="23"/>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="Z28" s="23"/>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2691,10 +2657,9 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="23"/>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="Z29" s="23"/>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2720,10 +2685,9 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
-      <c r="Z30" s="13"/>
-      <c r="AA30" s="23"/>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="Z30" s="23"/>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2749,10 +2713,9 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
-      <c r="Z31" s="13"/>
-      <c r="AA31" s="23"/>
-    </row>
-    <row r="32" spans="1:27">
+      <c r="Z31" s="23"/>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2778,10 +2741,9 @@
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
-      <c r="Z32" s="13"/>
-      <c r="AA32" s="23"/>
-    </row>
-    <row r="33" spans="1:27">
+      <c r="Z32" s="23"/>
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2807,10 +2769,9 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
-      <c r="Z33" s="13"/>
-      <c r="AA33" s="23"/>
-    </row>
-    <row r="34" spans="1:27">
+      <c r="Z33" s="23"/>
+    </row>
+    <row r="34" spans="1:26">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2836,8 +2797,7 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
-      <c r="Z34" s="13"/>
-      <c r="AA34" s="23"/>
+      <c r="Z34" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -2868,18 +2828,12 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$73:$A$311</xm:f>
           </x14:formula1>
           <xm:sqref>H1:H1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$315:$A$354</xm:f>
-          </x14:formula1>
-          <xm:sqref>X1:X1048576 X1</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\3.0.1\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\ZGBS-CP\feature-3.0.4\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息维护模板" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="374">
   <si>
     <t>登记银行代码*</t>
   </si>
@@ -1766,33 +1766,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.90625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="23.26953125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="27.6328125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="19.6328125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="17.36328125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.26953125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="10" customWidth="1"/>
+    <col min="5" max="5" width="27.625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.25" style="10" customWidth="1"/>
     <col min="9" max="9" width="19" style="10" customWidth="1"/>
-    <col min="10" max="10" width="14.08984375" style="10" customWidth="1"/>
-    <col min="11" max="11" width="31.6328125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="24.7265625" style="10" customWidth="1"/>
-    <col min="13" max="13" width="22.7265625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="23.26953125" style="10" customWidth="1"/>
-    <col min="15" max="15" width="23.36328125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="23.26953125" style="10" customWidth="1"/>
-    <col min="17" max="17" width="8.90625" style="10" customWidth="1"/>
-    <col min="18" max="18" width="10.90625" style="10" customWidth="1"/>
-    <col min="19" max="19" width="12.7265625" style="10" customWidth="1"/>
-    <col min="20" max="20" width="13.26953125" style="10" customWidth="1"/>
-    <col min="21" max="21" width="16.36328125" style="10" customWidth="1"/>
-    <col min="22" max="22" width="12.453125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="31.625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="24.75" style="10" customWidth="1"/>
+    <col min="13" max="13" width="22.75" style="10" customWidth="1"/>
+    <col min="14" max="14" width="23.25" style="10" customWidth="1"/>
+    <col min="15" max="15" width="23.375" style="10" customWidth="1"/>
+    <col min="16" max="16" width="23.25" style="10" customWidth="1"/>
+    <col min="17" max="17" width="8.875" style="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" style="10" customWidth="1"/>
+    <col min="19" max="19" width="12.75" style="10" customWidth="1"/>
+    <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
+    <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
     <col min="23" max="23" width="19" style="10" customWidth="1"/>
-    <col min="24" max="25" width="18.26953125" style="11" customWidth="1"/>
-    <col min="26" max="26" width="21.7265625" customWidth="1"/>
+    <col min="24" max="25" width="18.25" style="11" customWidth="1"/>
+    <col min="26" max="26" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21" customHeight="1">
@@ -2828,12 +2828,18 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$73:$A$311</xm:f>
           </x14:formula1>
           <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$356:$A$390</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2843,10 +2849,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A354"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:A390"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="100.7265625" customWidth="1"/>
+    <col min="1" max="1" width="100.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="33.75" customHeight="1">
@@ -4598,6 +4604,181 @@
     <row r="354" spans="1:1">
       <c r="A354" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
